--- a/data/trans_orig/IQ19B_A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ19B_A-Estudios-trans_orig.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>484</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>29341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1987,12 +1987,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>10945</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15443</t>
+          <t>15351</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21649</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>20355</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35860</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42282</t>
+          <t>42293</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>57476</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>52635</t>
+          <t>52209</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>68182</t>
+          <t>67848</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>100058</t>
+          <t>99987</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>120408</t>
+          <t>122486</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>66,54%</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24903</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>41187</t>
+          <t>40778</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>24523</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>32690</t>
+          <t>32509</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>43330</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,8%</t>
         </is>
       </c>
     </row>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4865,12 +4865,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>26303</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>28323</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>49469</t>
+          <t>50886</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>70195</t>
+          <t>70293</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>87670</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>83628</t>
+          <t>84313</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>103253</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>159535</t>
+          <t>159202</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>184425</t>
+          <t>184346</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>16873</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>31496</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>37834</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>57477</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -7757,12 +7757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -7868,12 +7868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>18527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19675</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29267</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7953,12 +7953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>432</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -8908,12 +8908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -8984,12 +8984,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9054,12 +9054,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -9095,12 +9095,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9130,12 +9130,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9145,12 +9145,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>12026</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>19588</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>17381</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33554</t>
+          <t>33575</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -9317,12 +9317,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42131</t>
+          <t>41849</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56797</t>
+          <t>56665</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9352,12 +9352,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>64937</t>
+          <t>66120</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>81221</t>
+          <t>81129</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9367,12 +9367,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>112962</t>
+          <t>112206</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>133561</t>
+          <t>134002</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -9428,12 +9428,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>19919</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18264</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32532</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9513,12 +9513,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10594,12 +10594,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -10655,12 +10655,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>451</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10725,12 +10725,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10740,12 +10740,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -10766,12 +10766,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>22298</t>
+          <t>22168</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10801,12 +10801,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10836,12 +10836,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>27207</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>40188</t>
+          <t>39897</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>11981</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>21369</t>
+          <t>21307</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>464</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>430</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>12181</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -12104,12 +12104,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12119,12 +12119,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12154,12 +12154,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>45055</t>
+          <t>45398</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -12215,12 +12215,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>73158</t>
+          <t>72736</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>91704</t>
+          <t>91961</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12230,12 +12230,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12250,12 +12250,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>91416</t>
+          <t>90049</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>109993</t>
+          <t>109756</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12265,12 +12265,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12285,12 +12285,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>169937</t>
+          <t>168769</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>197016</t>
+          <t>195874</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>27858</t>
+          <t>28848</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>15893</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>31148</t>
+          <t>31187</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>33871</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>54624</t>
+          <t>54409</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -13678,7 +13678,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -13784,12 +13784,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13819,12 +13819,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13834,12 +13834,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -13895,12 +13895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>12937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22167</t>
+          <t>21656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14041,12 +14041,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14056,12 +14056,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14091,12 +14091,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15157,12 +15157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15192,12 +15192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15207,12 +15207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -15233,12 +15233,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15248,12 +15248,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15268,12 +15268,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24734</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15283,12 +15283,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15303,12 +15303,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24295</t>
+          <t>24315</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42512</t>
+          <t>41228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15318,12 +15318,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>62465</t>
+          <t>62573</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>78883</t>
+          <t>79912</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>64522</t>
+          <t>65251</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>82236</t>
+          <t>82344</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>132051</t>
+          <t>133108</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>155735</t>
+          <t>157190</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -15455,12 +15455,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26829</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15470,12 +15470,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15490,12 +15490,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26715</t>
+          <t>28014</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15505,12 +15505,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15525,12 +15525,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48869</t>
+          <t>48994</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15540,12 +15540,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -16515,7 +16515,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -16571,12 +16571,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>555</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -16586,12 +16586,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -16641,12 +16641,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>560</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -16656,12 +16656,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -16682,12 +16682,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -16697,12 +16697,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -16717,12 +16717,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -16732,12 +16732,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -16767,12 +16767,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -16793,12 +16793,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>24644</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -16808,12 +16808,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -16828,12 +16828,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23656</t>
+          <t>23574</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -16843,12 +16843,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -16863,12 +16863,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>33735</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>46234</t>
+          <t>46032</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -16904,12 +16904,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -16919,12 +16919,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -16939,12 +16939,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -16954,12 +16954,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -16974,12 +16974,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -16989,12 +16989,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -17581,7 +17581,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -17803,7 +17803,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -17914,7 +17914,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -17944,12 +17944,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -17959,12 +17959,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -17979,12 +17979,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -17994,12 +17994,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -18020,12 +18020,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -18035,12 +18035,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -18055,12 +18055,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -18070,12 +18070,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -18090,12 +18090,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -18105,12 +18105,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -18131,12 +18131,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18146,12 +18146,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18166,12 +18166,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>30968</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18181,12 +18181,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -18201,12 +18201,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>52933</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -18216,12 +18216,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -18242,12 +18242,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>89325</t>
+          <t>89560</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>109473</t>
+          <t>108849</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -18257,12 +18257,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -18277,12 +18277,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>92716</t>
+          <t>92387</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>113008</t>
+          <t>113344</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -18292,12 +18292,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -18312,12 +18312,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>187732</t>
+          <t>188300</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>216330</t>
+          <t>217145</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -18327,12 +18327,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -18353,12 +18353,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -18368,12 +18368,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -18388,12 +18388,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -18403,12 +18403,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -18423,12 +18423,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>44720</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>66458</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -18438,12 +18438,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -18867,7 +18867,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -18887,7 +18887,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -18902,7 +18902,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -19775,7 +19775,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -19790,7 +19790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -19811,12 +19811,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -19826,12 +19826,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -19846,12 +19846,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -19861,12 +19861,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -19881,12 +19881,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -19896,12 +19896,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -19922,12 +19922,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -19937,12 +19937,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -19957,12 +19957,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -19972,12 +19972,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -19992,12 +19992,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>29677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -20007,12 +20007,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>73,74%</t>
         </is>
       </c>
     </row>
@@ -20033,12 +20033,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -20048,12 +20048,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -20068,12 +20068,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -20083,12 +20083,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -20103,12 +20103,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>18909</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -20118,12 +20118,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>46,98%</t>
         </is>
       </c>
     </row>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -20281,7 +20281,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -20351,7 +20351,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -20488,7 +20488,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -20503,7 +20503,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -20523,7 +20523,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -20538,7 +20538,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -20710,7 +20710,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -20725,7 +20725,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -20795,7 +20795,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -20932,7 +20932,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -20947,7 +20947,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -20997,12 +20997,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8742</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -21149,12 +21149,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -21164,12 +21164,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -21184,12 +21184,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>849</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -21204,7 +21204,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -21219,12 +21219,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -21234,12 +21234,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -21260,12 +21260,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27382</t>
+          <t>26861</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -21275,12 +21275,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -21295,12 +21295,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>19205</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>37419</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -21310,12 +21310,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -21330,12 +21330,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35093</t>
+          <t>35099</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58630</t>
+          <t>59382</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -21345,12 +21345,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -21371,12 +21371,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60751</t>
+          <t>59459</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>80524</t>
+          <t>79709</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -21386,12 +21386,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -21406,12 +21406,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>81812</t>
+          <t>82044</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106447</t>
+          <t>106298</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -21421,12 +21421,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -21441,12 +21441,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>148342</t>
+          <t>149212</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>180390</t>
+          <t>181045</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -21456,12 +21456,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,56%</t>
         </is>
       </c>
     </row>
@@ -21482,12 +21482,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>25625</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42460</t>
+          <t>41674</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -21497,12 +21497,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -21517,12 +21517,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>26061</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46467</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -21532,12 +21532,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -21552,12 +21552,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56220</t>
+          <t>56260</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>83271</t>
+          <t>83052</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -21567,12 +21567,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -22527,7 +22527,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -22542,7 +22542,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -22603,7 +22603,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -22653,7 +22653,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -22668,12 +22668,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -22683,12 +22683,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -22709,12 +22709,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -22724,12 +22724,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -22744,12 +22744,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -22759,12 +22759,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -22779,12 +22779,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -22794,12 +22794,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -22820,12 +22820,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>24895</t>
+          <t>24912</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -22835,12 +22835,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -22855,12 +22855,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20432</t>
+          <t>19841</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>35694</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -22870,12 +22870,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>37364</t>
+          <t>37719</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>55966</t>
+          <t>56578</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -22905,12 +22905,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -22931,12 +22931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>12704</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -22946,12 +22946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -22966,12 +22966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>32008</t>
+          <t>32235</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -22981,12 +22981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -23001,12 +23001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32314</t>
+          <t>32521</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>51800</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -23016,12 +23016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,16%</t>
         </is>
       </c>
     </row>
@@ -23164,7 +23164,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -23214,7 +23214,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -23234,7 +23234,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -23249,7 +23249,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -23386,7 +23386,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -23401,7 +23401,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -23421,7 +23421,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -23436,7 +23436,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -23608,7 +23608,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -23623,44 +23623,44 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>4740</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -23678,7 +23678,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -23693,7 +23693,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -23754,7 +23754,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -23769,7 +23769,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -23830,7 +23830,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -23865,7 +23865,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -23880,7 +23880,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -23895,12 +23895,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -23910,12 +23910,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -23976,7 +23976,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -24011,7 +24011,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -24047,12 +24047,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -24062,12 +24062,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -24082,12 +24082,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -24097,12 +24097,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -24117,12 +24117,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -24137,7 +24137,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -24158,12 +24158,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>32707</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -24173,12 +24173,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -24193,12 +24193,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>26712</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>45898</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -24208,12 +24208,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -24228,12 +24228,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>48095</t>
+          <t>48014</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>74192</t>
+          <t>73042</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -24243,12 +24243,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -24269,12 +24269,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>91543</t>
+          <t>90212</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>117446</t>
+          <t>115740</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -24284,49 +24284,49 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
+          <t>59,6%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>131210</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>115297</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>145121</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>54,68%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>48,05%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
           <t>60,47%</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>131210</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>115413</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>144540</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>54,68%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>296</t>
@@ -24339,12 +24339,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>216694</t>
+          <t>215412</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>256476</t>
+          <t>255025</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -24354,12 +24354,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,74%</t>
         </is>
       </c>
     </row>
@@ -24380,12 +24380,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>69162</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -24395,12 +24395,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -24415,12 +24415,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>49660</t>
+          <t>49888</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>77926</t>
+          <t>78583</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -24430,12 +24430,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -24450,12 +24450,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>102820</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>139082</t>
+          <t>139339</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -24465,12 +24465,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
